--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:08</t>
+    <t xml:space="preserve">2026-09-09 23:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:02</t>
+    <t xml:space="preserve">2026-09-17 13:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:59</t>
+    <t xml:space="preserve">2026-09-23 12:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:28</t>
+    <t xml:space="preserve">2026-10-02 13:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:46</t>
+    <t xml:space="preserve">2026-10-05 10:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -585,7 +585,7 @@
         <v>2020</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>751081.62</v>
+        <v>751081.63</v>
       </c>
     </row>
     <row r="4">
@@ -602,7 +602,7 @@
         <v>2020</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>745679.12</v>
+        <v>745679.13</v>
       </c>
     </row>
     <row r="5">
@@ -704,7 +704,7 @@
         <v>2020</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>674925.12</v>
+        <v>674925.13</v>
       </c>
     </row>
     <row r="11">
@@ -857,7 +857,7 @@
         <v>2020</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>624600.12</v>
+        <v>624600.13</v>
       </c>
     </row>
     <row r="20">
